--- a/separated_by_section/Complaint_and_Dispute_Resolution.xlsx
+++ b/separated_by_section/Complaint_and_Dispute_Resolution.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P149"/>
+  <dimension ref="A1:P251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -10671,6 +10671,7030 @@
         </is>
       </c>
     </row>
+    <row r="150">
+      <c r="A150" s="1" t="n">
+        <v>570725</v>
+      </c>
+      <c r="B150" s="1" t="inlineStr">
+        <is>
+          <t>New refund regulations</t>
+        </is>
+      </c>
+      <c r="C150" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/content/new-refund-regulations</t>
+        </is>
+      </c>
+      <c r="D150" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/content/nouveau-reglement-concernant-remboursements</t>
+        </is>
+      </c>
+      <c r="E150" s="1" t="inlineStr">
+        <is>
+          <t>Wednesday, June 22, 2022</t>
+        </is>
+      </c>
+      <c r="F150" s="1" t="n">
+        <v>2026</v>
+      </c>
+      <c r="G150" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H150" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I150" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J150" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K150" s="1" t="inlineStr"/>
+      <c r="L150" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="M150" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="N150" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O150" s="1" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="P150" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="n">
+        <v>568479</v>
+      </c>
+      <c r="B151" s="1" t="inlineStr">
+        <is>
+          <t>Advisories for Pakistan and certain regions in India</t>
+        </is>
+      </c>
+      <c r="C151" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/content/advisories-pakistan-and-certain-regions-india</t>
+        </is>
+      </c>
+      <c r="D151" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/content/avis-voyage-pour-pakistan-et-certaines-regions-linde</t>
+        </is>
+      </c>
+      <c r="E151" s="1" t="inlineStr">
+        <is>
+          <t>Wednesday, February 27, 2019</t>
+        </is>
+      </c>
+      <c r="F151" s="1" t="n">
+        <v>2026</v>
+      </c>
+      <c r="G151" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H151" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I151" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J151" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K151" s="1" t="inlineStr"/>
+      <c r="L151" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="M151" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="N151" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="O151" s="1" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="P151" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="n">
+        <v>568000</v>
+      </c>
+      <c r="B152" s="1" t="inlineStr">
+        <is>
+          <t>What you should know if you were affected by the cancelled Montreal LEVEL flights</t>
+        </is>
+      </c>
+      <c r="C152" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/content/what-you-should-know-if-you-were-affected-cancelled-montreal-level-flights</t>
+        </is>
+      </c>
+      <c r="D152" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/content/ce-que-vous-devez-savoir-si-vous-avez-ete-affecte-par-annulations-vols-level-a-montreal</t>
+        </is>
+      </c>
+      <c r="E152" s="1" t="inlineStr">
+        <is>
+          <t>Tuesday, July 17, 2018</t>
+        </is>
+      </c>
+      <c r="F152" s="1" t="n">
+        <v>2026</v>
+      </c>
+      <c r="G152" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H152" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I152" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J152" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K152" s="1" t="inlineStr"/>
+      <c r="L152" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="M152" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="N152" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="O152" s="1" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="P152" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="n">
+        <v>572211</v>
+      </c>
+      <c r="B153" s="1" t="inlineStr">
+        <is>
+          <t>Our mandate</t>
+        </is>
+      </c>
+      <c r="C153" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/our-organization/our-mandate</t>
+        </is>
+      </c>
+      <c r="D153" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/notre-organisme/notre-mandat</t>
+        </is>
+      </c>
+      <c r="E153" s="1" t="inlineStr">
+        <is>
+          <t>Wednesday, December 20, 2023</t>
+        </is>
+      </c>
+      <c r="F153" s="1" t="n">
+        <v>2026</v>
+      </c>
+      <c r="G153" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H153" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I153" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J153" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K153" s="1" t="inlineStr"/>
+      <c r="L153" s="1" t="n">
+        <v>977</v>
+      </c>
+      <c r="M153" s="1" t="n">
+        <v>1213</v>
+      </c>
+      <c r="N153" s="1" t="n">
+        <v>1260</v>
+      </c>
+      <c r="O153" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P153" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="n">
+        <v>569789</v>
+      </c>
+      <c r="B154" s="1" t="inlineStr">
+        <is>
+          <t>FAQs - Consultation on new refund requirements</t>
+        </is>
+      </c>
+      <c r="C154" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/faqs-consultation-new-refund-requirements</t>
+        </is>
+      </c>
+      <c r="D154" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/faq-consultation-sur-nouvelles-exigences-remboursement</t>
+        </is>
+      </c>
+      <c r="E154" s="1" t="inlineStr">
+        <is>
+          <t>Monday, December 21, 2020</t>
+        </is>
+      </c>
+      <c r="F154" s="1" t="n">
+        <v>2026</v>
+      </c>
+      <c r="G154" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H154" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I154" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J154" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K154" s="1" t="inlineStr"/>
+      <c r="L154" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="M154" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="N154" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="O154" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P154" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="n">
+        <v>569178</v>
+      </c>
+      <c r="B155" s="1" t="inlineStr">
+        <is>
+          <t>Statement on Vouchers</t>
+        </is>
+      </c>
+      <c r="C155" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/statement-vouchers</t>
+        </is>
+      </c>
+      <c r="D155" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/message-concernant-credits</t>
+        </is>
+      </c>
+      <c r="E155" s="1" t="inlineStr">
+        <is>
+          <t>Wednesday, March 25, 2020</t>
+        </is>
+      </c>
+      <c r="F155" s="1" t="n">
+        <v>2026</v>
+      </c>
+      <c r="G155" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H155" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I155" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J155" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K155" s="1" t="inlineStr"/>
+      <c r="L155" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="M155" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="N155" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="O155" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P155" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="n">
+        <v>418225</v>
+      </c>
+      <c r="B156" s="1" t="inlineStr">
+        <is>
+          <t>Baggage</t>
+        </is>
+      </c>
+      <c r="C156" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/baggage</t>
+        </is>
+      </c>
+      <c r="D156" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/bagages</t>
+        </is>
+      </c>
+      <c r="E156" s="1" t="inlineStr">
+        <is>
+          <t>Friday, October 14, 2016</t>
+        </is>
+      </c>
+      <c r="F156" s="1" t="n">
+        <v>2026</v>
+      </c>
+      <c r="G156" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H156" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I156" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J156" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K156" s="1" t="inlineStr"/>
+      <c r="L156" s="1" t="n">
+        <v>599</v>
+      </c>
+      <c r="M156" s="1" t="n">
+        <v>699</v>
+      </c>
+      <c r="N156" s="1" t="n">
+        <v>671</v>
+      </c>
+      <c r="O156" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P156" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="n">
+        <v>281774</v>
+      </c>
+      <c r="B157" s="1" t="inlineStr">
+        <is>
+          <t>Service standards of the Agency</t>
+        </is>
+      </c>
+      <c r="C157" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/service-standards-agency</t>
+        </is>
+      </c>
+      <c r="D157" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/normes-service-loffice</t>
+        </is>
+      </c>
+      <c r="E157" s="1" t="inlineStr">
+        <is>
+          <t>Wednesday, January 7, 2026</t>
+        </is>
+      </c>
+      <c r="F157" s="1" t="n">
+        <v>2026</v>
+      </c>
+      <c r="G157" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H157" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I157" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J157" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K157" s="1" t="inlineStr"/>
+      <c r="L157" s="1" t="n">
+        <v>83</v>
+      </c>
+      <c r="M157" s="1" t="n">
+        <v>117</v>
+      </c>
+      <c r="N157" s="1" t="n">
+        <v>124</v>
+      </c>
+      <c r="O157" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P157" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="n">
+        <v>100120</v>
+      </c>
+      <c r="B158" s="1" t="inlineStr">
+        <is>
+          <t>Transparency</t>
+        </is>
+      </c>
+      <c r="C158" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/transparency</t>
+        </is>
+      </c>
+      <c r="D158" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/transparence</t>
+        </is>
+      </c>
+      <c r="E158" s="1" t="inlineStr">
+        <is>
+          <t>Friday, June 6, 2025</t>
+        </is>
+      </c>
+      <c r="F158" s="1" t="n">
+        <v>2026</v>
+      </c>
+      <c r="G158" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H158" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I158" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J158" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K158" s="1" t="inlineStr"/>
+      <c r="L158" s="1" t="n">
+        <v>376</v>
+      </c>
+      <c r="M158" s="1" t="n">
+        <v>454</v>
+      </c>
+      <c r="N158" s="1" t="n">
+        <v>417</v>
+      </c>
+      <c r="O158" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P158" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="n">
+        <v>572323</v>
+      </c>
+      <c r="B159" s="1" t="inlineStr">
+        <is>
+          <t>Lynx Air passengers - Important information about cessation of air operations</t>
+        </is>
+      </c>
+      <c r="C159" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/content/lynx-air-passengers-important-information-about-cessation-air-operations</t>
+        </is>
+      </c>
+      <c r="D159" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/content/passagers-lynx-air-informations-importantes-concernant-cessation-des-operations-aeriennes</t>
+        </is>
+      </c>
+      <c r="E159" s="1" t="inlineStr">
+        <is>
+          <t>Tuesday, February 27, 2024</t>
+        </is>
+      </c>
+      <c r="F159" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G159" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H159" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I159" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J159" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K159" s="1" t="inlineStr"/>
+      <c r="L159" s="1" t="n">
+        <v>121</v>
+      </c>
+      <c r="M159" s="1" t="n">
+        <v>134</v>
+      </c>
+      <c r="N159" s="1" t="n">
+        <v>130</v>
+      </c>
+      <c r="O159" s="1" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="P159" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="n">
+        <v>570123</v>
+      </c>
+      <c r="B160" s="1" t="inlineStr">
+        <is>
+          <t>Proposed new refund requirements open for public review and comment</t>
+        </is>
+      </c>
+      <c r="C160" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/content/proposed-new-refund-requirements-open-public-review-and-comment</t>
+        </is>
+      </c>
+      <c r="D160" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/content/publication-dune-proposition-nouvelles-exigences-remboursement-aux-fins-dexamen-et</t>
+        </is>
+      </c>
+      <c r="E160" s="1" t="inlineStr">
+        <is>
+          <t>Friday, July 2, 2021</t>
+        </is>
+      </c>
+      <c r="F160" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G160" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H160" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I160" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J160" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K160" s="1" t="inlineStr"/>
+      <c r="L160" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="M160" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="N160" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="O160" s="1" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="P160" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="n">
+        <v>569972</v>
+      </c>
+      <c r="B161" s="1" t="inlineStr">
+        <is>
+          <t>How the CTA will be processing refund-related complaints resulting from the pandemic</t>
+        </is>
+      </c>
+      <c r="C161" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/content/how-cta-will-be-processing-refund-related-complaints-resulting-from-pandemic</t>
+        </is>
+      </c>
+      <c r="D161" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/content/comment-lotc-traitera-plaintes-liees-a-des-remboursements-raison-pandemie</t>
+        </is>
+      </c>
+      <c r="E161" s="1" t="inlineStr">
+        <is>
+          <t>Tuesday, July 13, 2021</t>
+        </is>
+      </c>
+      <c r="F161" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G161" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H161" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I161" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J161" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K161" s="1" t="inlineStr"/>
+      <c r="L161" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="M161" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="N161" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="O161" s="1" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="P161" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="n">
+        <v>569877</v>
+      </c>
+      <c r="B162" s="1" t="inlineStr">
+        <is>
+          <t>Proposed Accessible Transportation Planning and Reporting Regulations now open for public review and comments</t>
+        </is>
+      </c>
+      <c r="C162" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/content/proposed-accessible-transportation-planning-and-reporting-regulations-now-open-public-review</t>
+        </is>
+      </c>
+      <c r="D162" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/content/projet-reglement-sur-letablissement-des-plans-et-des-rapports-matiere-transports-accessibles</t>
+        </is>
+      </c>
+      <c r="E162" s="1" t="inlineStr">
+        <is>
+          <t>Saturday, February 13, 2021</t>
+        </is>
+      </c>
+      <c r="F162" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G162" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H162" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I162" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J162" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K162" s="1" t="inlineStr"/>
+      <c r="L162" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="M162" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="N162" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="O162" s="1" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="P162" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="n">
+        <v>569767</v>
+      </c>
+      <c r="B163" s="1" t="inlineStr">
+        <is>
+          <t>CTA Holds Public Consultation on Requests for Temporary Adjustments to the Requirements of the Air Passenger Protection Regulations</t>
+        </is>
+      </c>
+      <c r="C163" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/content/cta-holds-public-consultation-requests-temporary-adjustments-requirements-air-passenger</t>
+        </is>
+      </c>
+      <c r="D163" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/content/lotc-tient-une-consultation-publique-sur-demandes-modification-temporaire-des-exigences</t>
+        </is>
+      </c>
+      <c r="E163" s="1" t="inlineStr">
+        <is>
+          <t>Friday, December 11, 2020</t>
+        </is>
+      </c>
+      <c r="F163" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G163" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H163" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I163" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J163" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K163" s="1" t="inlineStr"/>
+      <c r="L163" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="M163" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="N163" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="O163" s="1" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="P163" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="n">
+        <v>569004</v>
+      </c>
+      <c r="B164" s="1" t="inlineStr">
+        <is>
+          <t>New provisions of Air Passenger Protection Regulations coming into force</t>
+        </is>
+      </c>
+      <c r="C164" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/content/new-provisions-air-passenger-protection-regulations-coming-force</t>
+        </is>
+      </c>
+      <c r="D164" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/content/entree-vigueur-nouvelles-dispositions-reglement-sur-protection-des-passagers-aeriens</t>
+        </is>
+      </c>
+      <c r="E164" s="1" t="inlineStr">
+        <is>
+          <t>Friday, December 13, 2019</t>
+        </is>
+      </c>
+      <c r="F164" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G164" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H164" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I164" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J164" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K164" s="1" t="inlineStr"/>
+      <c r="L164" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="M164" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="N164" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="O164" s="1" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="P164" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="n">
+        <v>568801</v>
+      </c>
+      <c r="B165" s="1" t="inlineStr">
+        <is>
+          <t>Canadian Transportation Agency launches inquiry into WestJet flight incident</t>
+        </is>
+      </c>
+      <c r="C165" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/content/canadian-transportation-agency-launches-inquiry-westjet-flight-incident</t>
+        </is>
+      </c>
+      <c r="D165" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/content/incident-mettant-cause-un-vol-westjet-loffice-des-transports-canada-lance-une-enquete</t>
+        </is>
+      </c>
+      <c r="E165" s="1" t="inlineStr">
+        <is>
+          <t>Friday, August 16, 2019</t>
+        </is>
+      </c>
+      <c r="F165" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G165" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H165" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I165" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J165" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K165" s="1" t="inlineStr"/>
+      <c r="L165" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="M165" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="N165" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="O165" s="1" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="P165" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="n">
+        <v>573065</v>
+      </c>
+      <c r="B166" s="1" t="inlineStr">
+        <is>
+          <t>Plan ministériel 2025-2026 de l’Office des transports du Canada : En un coup d’œil</t>
+        </is>
+      </c>
+      <c r="C166" s="1" t="inlineStr"/>
+      <c r="D166" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/publication/office-des-transports-du-canada-plan-ministeriel-2025-2026-en-un-coup-d-oeil</t>
+        </is>
+      </c>
+      <c r="E166" s="1" t="inlineStr">
+        <is>
+          <t>Tuesday, June 17, 2025</t>
+        </is>
+      </c>
+      <c r="F166" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G166" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H166" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I166" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J166" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K166" s="1" t="inlineStr">
+        <is>
+          <t>Missing EN</t>
+        </is>
+      </c>
+      <c r="L166" s="1" t="inlineStr"/>
+      <c r="M166" s="1" t="inlineStr"/>
+      <c r="N166" s="1" t="inlineStr"/>
+      <c r="O166" s="1" t="inlineStr">
+        <is>
+          <t>Publication</t>
+        </is>
+      </c>
+      <c r="P166" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="n">
+        <v>570853</v>
+      </c>
+      <c r="B167" s="1" t="inlineStr">
+        <is>
+          <t>Quarterly Financial Report for the quarter ended June 30, 2022</t>
+        </is>
+      </c>
+      <c r="C167" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/publication/quarterly-financial-report-quarter-ended-june-30-2022</t>
+        </is>
+      </c>
+      <c r="D167" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/publication/rapport-financier-trimestriel-pour-trimestre-termine-30-juin-2022</t>
+        </is>
+      </c>
+      <c r="E167" s="1" t="inlineStr">
+        <is>
+          <t>Thursday, September 1, 2022</t>
+        </is>
+      </c>
+      <c r="F167" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G167" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H167" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I167" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J167" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K167" s="1" t="inlineStr"/>
+      <c r="L167" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="M167" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="N167" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="O167" s="1" t="inlineStr">
+        <is>
+          <t>Publication</t>
+        </is>
+      </c>
+      <c r="P167" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="n">
+        <v>570530</v>
+      </c>
+      <c r="B168" s="1" t="inlineStr">
+        <is>
+          <t>Quarterly Financial Report for the quarter ended December 31, 2021</t>
+        </is>
+      </c>
+      <c r="C168" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/publication/quarterly-financial-report-quarter-ended-december-31-2021</t>
+        </is>
+      </c>
+      <c r="D168" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/publication/rapport-financier-trimestriel-pour-trimestre-termine-31-decembre-2021</t>
+        </is>
+      </c>
+      <c r="E168" s="1" t="inlineStr">
+        <is>
+          <t>Wednesday, March 2, 2022</t>
+        </is>
+      </c>
+      <c r="F168" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G168" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H168" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I168" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J168" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K168" s="1" t="inlineStr"/>
+      <c r="L168" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="M168" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="N168" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="O168" s="1" t="inlineStr">
+        <is>
+          <t>Publication</t>
+        </is>
+      </c>
+      <c r="P168" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="n">
+        <v>569143</v>
+      </c>
+      <c r="B169" s="1" t="inlineStr">
+        <is>
+          <t>Quarterly Financial Report for the quarter ended December 31, 2019</t>
+        </is>
+      </c>
+      <c r="C169" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/publication/quarterly-financial-report-quarter-ended-december-31-2019</t>
+        </is>
+      </c>
+      <c r="D169" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/publication/rapport-financier-trimestriel-pour-trimestre-termine-31-decembre-2019</t>
+        </is>
+      </c>
+      <c r="E169" s="1" t="inlineStr">
+        <is>
+          <t>Friday, February 28, 2020</t>
+        </is>
+      </c>
+      <c r="F169" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G169" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H169" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I169" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J169" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K169" s="1" t="inlineStr"/>
+      <c r="L169" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="M169" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="N169" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="O169" s="1" t="inlineStr">
+        <is>
+          <t>Publication</t>
+        </is>
+      </c>
+      <c r="P169" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="n">
+        <v>568812</v>
+      </c>
+      <c r="B170" s="1" t="inlineStr">
+        <is>
+          <t>Quarterly Financial Report for the quarter ended June 30, 2019</t>
+        </is>
+      </c>
+      <c r="C170" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/publication/quarterly-financial-report-quarter-ended-june-30-2019</t>
+        </is>
+      </c>
+      <c r="D170" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/publication/rapport-financier-trimestriel-pour-trimestre-termine-30-juin-2019</t>
+        </is>
+      </c>
+      <c r="E170" s="1" t="inlineStr">
+        <is>
+          <t>Wednesday, August 28, 2019</t>
+        </is>
+      </c>
+      <c r="F170" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G170" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H170" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I170" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J170" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K170" s="1" t="inlineStr"/>
+      <c r="L170" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="M170" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="N170" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="O170" s="1" t="inlineStr">
+        <is>
+          <t>Publication</t>
+        </is>
+      </c>
+      <c r="P170" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="n">
+        <v>568789</v>
+      </c>
+      <c r="B171" s="1" t="inlineStr">
+        <is>
+          <t>Agency Evaluation Plan 2019-20 to 2023-24</t>
+        </is>
+      </c>
+      <c r="C171" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/publication/agency-evaluation-plan-2019-20-2023-24</t>
+        </is>
+      </c>
+      <c r="D171" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/publication/plan-devaluation-loffice-2019-2020-a-2023-2024</t>
+        </is>
+      </c>
+      <c r="E171" s="1" t="inlineStr">
+        <is>
+          <t>Tuesday, August 6, 2019</t>
+        </is>
+      </c>
+      <c r="F171" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G171" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H171" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I171" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J171" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K171" s="1" t="inlineStr"/>
+      <c r="L171" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="M171" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="N171" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="O171" s="1" t="inlineStr">
+        <is>
+          <t>Publication</t>
+        </is>
+      </c>
+      <c r="P171" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="n">
+        <v>97548</v>
+      </c>
+      <c r="B172" s="1" t="inlineStr">
+        <is>
+          <t>What is Mediation?</t>
+        </is>
+      </c>
+      <c r="C172" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/publication/what-mediation</t>
+        </is>
+      </c>
+      <c r="D172" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/publication/quest-ce-que-mediation</t>
+        </is>
+      </c>
+      <c r="E172" s="1" t="inlineStr">
+        <is>
+          <t>Tuesday, May 6, 2025</t>
+        </is>
+      </c>
+      <c r="F172" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G172" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H172" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I172" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J172" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K172" s="1" t="inlineStr"/>
+      <c r="L172" s="1" t="n">
+        <v>160</v>
+      </c>
+      <c r="M172" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="N172" s="1" t="n">
+        <v>199</v>
+      </c>
+      <c r="O172" s="1" t="inlineStr">
+        <is>
+          <t>Publication</t>
+        </is>
+      </c>
+      <c r="P172" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="n">
+        <v>571624</v>
+      </c>
+      <c r="B173" s="1" t="inlineStr">
+        <is>
+          <t>Opening remarks from Ms. France Pégeot (Chair and Chief Executive Officer, Canadian Transportation Agency) to the Standing Committee on Transport, Infrastructure and Communities - January 12, 2023</t>
+        </is>
+      </c>
+      <c r="C173" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/content/opening-remarks-ms-france-pegeot-chair-and-chief-executive-officer-canadian-transportation</t>
+        </is>
+      </c>
+      <c r="D173" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/contenu/allocution-douverture-mme-france-pegeot-presidente-et-premiere-dirigeante-office-des</t>
+        </is>
+      </c>
+      <c r="E173" s="1" t="inlineStr">
+        <is>
+          <t>Thursday, January 12, 2023</t>
+        </is>
+      </c>
+      <c r="F173" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G173" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H173" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I173" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J173" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K173" s="1" t="inlineStr"/>
+      <c r="L173" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="M173" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="N173" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="O173" s="1" t="inlineStr">
+        <is>
+          <t>Speeches</t>
+        </is>
+      </c>
+      <c r="P173" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="n">
+        <v>573318</v>
+      </c>
+      <c r="B174" s="1" t="inlineStr">
+        <is>
+          <t>Commentaires : Consultations sur la proposition de frais pour les plaintes relatives au transport aérien</t>
+        </is>
+      </c>
+      <c r="C174" s="1" t="inlineStr"/>
+      <c r="D174" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/commentaires-consultations-sur-proposition-frais-pour-plaintes-relatives-au-transport-aerien</t>
+        </is>
+      </c>
+      <c r="E174" s="1" t="inlineStr">
+        <is>
+          <t>Tuesday, December 9, 2025</t>
+        </is>
+      </c>
+      <c r="F174" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G174" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H174" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I174" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J174" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K174" s="1" t="inlineStr">
+        <is>
+          <t>Missing EN</t>
+        </is>
+      </c>
+      <c r="L174" s="1" t="inlineStr"/>
+      <c r="M174" s="1" t="inlineStr"/>
+      <c r="N174" s="1" t="inlineStr"/>
+      <c r="O174" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P174" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="n">
+        <v>573298</v>
+      </c>
+      <c r="B175" s="1" t="inlineStr">
+        <is>
+          <t>Air travel complaints per 100 flights – by airline – July 2024 to June 2025</t>
+        </is>
+      </c>
+      <c r="C175" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/air-travel-complaints-100-flights-airline-july-2024-june-2025</t>
+        </is>
+      </c>
+      <c r="D175" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/nombre-plaintes-aeriennes-par-100-vols-par-compagnie-aerienne-juillet-2024-a-juin-2025</t>
+        </is>
+      </c>
+      <c r="E175" s="1" t="inlineStr">
+        <is>
+          <t>Friday, November 28, 2025</t>
+        </is>
+      </c>
+      <c r="F175" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G175" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H175" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I175" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J175" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K175" s="1" t="inlineStr"/>
+      <c r="L175" s="1" t="n">
+        <v>491</v>
+      </c>
+      <c r="M175" s="1" t="n">
+        <v>548</v>
+      </c>
+      <c r="N175" s="1" t="n">
+        <v>550</v>
+      </c>
+      <c r="O175" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P175" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="n">
+        <v>572984</v>
+      </c>
+      <c r="B176" s="1" t="inlineStr">
+        <is>
+          <t>Air travel complaints per 100 flights – by airline – January 2024 to March 2025</t>
+        </is>
+      </c>
+      <c r="C176" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/air-travel-complaints-100-flights-airline-january-2024-march-2025</t>
+        </is>
+      </c>
+      <c r="D176" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/nombre-plaintes-aeriennes-par-100-vols-par-compagnie-aerienne-janvier-2024-a-mars-2025</t>
+        </is>
+      </c>
+      <c r="E176" s="1" t="inlineStr">
+        <is>
+          <t>Wednesday, April 30, 2025</t>
+        </is>
+      </c>
+      <c r="F176" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G176" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H176" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I176" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J176" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K176" s="1" t="inlineStr"/>
+      <c r="L176" s="1" t="n">
+        <v>1000</v>
+      </c>
+      <c r="M176" s="1" t="n">
+        <v>1212</v>
+      </c>
+      <c r="N176" s="1" t="n">
+        <v>1210</v>
+      </c>
+      <c r="O176" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P176" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="n">
+        <v>572878</v>
+      </c>
+      <c r="B177" s="1" t="inlineStr">
+        <is>
+          <t>Air travel complaints per 100 flights – by airline – October 2023 to December 2024</t>
+        </is>
+      </c>
+      <c r="C177" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/air-travel-complaints-100-flights-airline-october-2023-december-2024</t>
+        </is>
+      </c>
+      <c r="D177" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/nombre-plaintes-aeriennes-par-100-vols-par-compagnie-aerienne-octobre-2023-a-decembre-2024</t>
+        </is>
+      </c>
+      <c r="E177" s="1" t="inlineStr">
+        <is>
+          <t>Monday, February 10, 2025</t>
+        </is>
+      </c>
+      <c r="F177" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G177" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H177" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I177" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J177" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K177" s="1" t="inlineStr"/>
+      <c r="L177" s="1" t="n">
+        <v>274</v>
+      </c>
+      <c r="M177" s="1" t="n">
+        <v>305</v>
+      </c>
+      <c r="N177" s="1" t="n">
+        <v>310</v>
+      </c>
+      <c r="O177" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P177" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="1" t="n">
+        <v>572756</v>
+      </c>
+      <c r="B178" s="1" t="inlineStr">
+        <is>
+          <t>Canadian Transportation Agency's 2023–24 Departmental results report: At a glance</t>
+        </is>
+      </c>
+      <c r="C178" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/canadian-transportation-agencys-2023-24-departmental-results-report-at-a-glance</t>
+        </is>
+      </c>
+      <c r="D178" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/rapport-sur-resultats-ministeriels-2023-2024-loffice-des-transports-canada-un-coup-doeil</t>
+        </is>
+      </c>
+      <c r="E178" s="1" t="inlineStr">
+        <is>
+          <t>Tuesday, December 17, 2024</t>
+        </is>
+      </c>
+      <c r="F178" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G178" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H178" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I178" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J178" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K178" s="1" t="inlineStr"/>
+      <c r="L178" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="M178" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="N178" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="O178" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P178" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="1" t="n">
+        <v>572604</v>
+      </c>
+      <c r="B179" s="1" t="inlineStr">
+        <is>
+          <t>Air travel complaints per 100 flights – by airline – April 2023 to June 2024</t>
+        </is>
+      </c>
+      <c r="C179" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/air-travel-complaints-100-flights-airline-april-2023-june-2024</t>
+        </is>
+      </c>
+      <c r="D179" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/nombre-plaintes-aeriennes-par-100-vols-par-compagnie-aerienne-avril-2023-a-juin-2024</t>
+        </is>
+      </c>
+      <c r="E179" s="1" t="inlineStr">
+        <is>
+          <t>Thursday, August 1, 2024</t>
+        </is>
+      </c>
+      <c r="F179" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G179" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H179" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I179" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J179" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K179" s="1" t="inlineStr"/>
+      <c r="L179" s="1" t="n">
+        <v>71</v>
+      </c>
+      <c r="M179" s="1" t="n">
+        <v>74</v>
+      </c>
+      <c r="N179" s="1" t="n">
+        <v>76</v>
+      </c>
+      <c r="O179" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P179" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="1" t="n">
+        <v>572114</v>
+      </c>
+      <c r="B180" s="1" t="inlineStr">
+        <is>
+          <t>Air travel complaints per 100 flights – by airline – July 2022 to September 2023</t>
+        </is>
+      </c>
+      <c r="C180" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/air-travel-complaints-100-flights-airline-july-2022-september-2023</t>
+        </is>
+      </c>
+      <c r="D180" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/nombre-plaintes-aeriennes-par-100-vols-par-compagnie-aerienne-juillet-2022-a-septembre-2023</t>
+        </is>
+      </c>
+      <c r="E180" s="1" t="inlineStr">
+        <is>
+          <t>Wednesday, November 8, 2023</t>
+        </is>
+      </c>
+      <c r="F180" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G180" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H180" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I180" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J180" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K180" s="1" t="inlineStr"/>
+      <c r="L180" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="M180" s="1" t="n">
+        <v>39</v>
+      </c>
+      <c r="N180" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="O180" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P180" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="1" t="n">
+        <v>571223</v>
+      </c>
+      <c r="B181" s="1" t="inlineStr">
+        <is>
+          <t>Air travel complaints per 100 flights – by airline</t>
+        </is>
+      </c>
+      <c r="C181" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/air-travel-complaints-100-flights-airline</t>
+        </is>
+      </c>
+      <c r="D181" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/nombre-plaintes-relatives-au-transport-aerien-par-100-vols-par-compagnie-aerienne</t>
+        </is>
+      </c>
+      <c r="E181" s="1" t="inlineStr">
+        <is>
+          <t>Friday, November 28, 2025</t>
+        </is>
+      </c>
+      <c r="F181" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G181" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H181" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I181" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J181" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K181" s="1" t="inlineStr"/>
+      <c r="L181" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="M181" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="N181" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O181" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P181" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="1" t="n">
+        <v>570670</v>
+      </c>
+      <c r="B182" s="1" t="inlineStr">
+        <is>
+          <t>Strategic Framework 2021-2025 – Proud of our history, ready for the future</t>
+        </is>
+      </c>
+      <c r="C182" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/strategic-framework-2021-2025-proud-our-history-ready-future</t>
+        </is>
+      </c>
+      <c r="D182" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/cadre-strategique-2021-2025-lotc-fiers-notre-histoire-prets-pour-lavenir</t>
+        </is>
+      </c>
+      <c r="E182" s="1" t="inlineStr">
+        <is>
+          <t>Monday, March 3, 2025</t>
+        </is>
+      </c>
+      <c r="F182" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G182" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H182" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I182" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J182" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K182" s="1" t="inlineStr"/>
+      <c r="L182" s="1" t="n">
+        <v>199</v>
+      </c>
+      <c r="M182" s="1" t="n">
+        <v>242</v>
+      </c>
+      <c r="N182" s="1" t="n">
+        <v>225</v>
+      </c>
+      <c r="O182" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P182" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="1" t="n">
+        <v>570122</v>
+      </c>
+      <c r="B183" s="1" t="inlineStr">
+        <is>
+          <t>Highlights of Proposed Airline Refund Requirements</t>
+        </is>
+      </c>
+      <c r="C183" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/highlights-proposed-airline-refund-requirements</t>
+        </is>
+      </c>
+      <c r="D183" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/apercu-des-exigences-remboursement-proposees-pour-compagnies-aeriennes</t>
+        </is>
+      </c>
+      <c r="E183" s="1" t="inlineStr">
+        <is>
+          <t>Friday, July 2, 2021</t>
+        </is>
+      </c>
+      <c r="F183" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G183" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H183" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I183" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J183" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K183" s="1" t="inlineStr"/>
+      <c r="L183" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="M183" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="N183" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="O183" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P183" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="1" t="n">
+        <v>100007</v>
+      </c>
+      <c r="B184" s="1" t="inlineStr">
+        <is>
+          <t>Performance and statistics</t>
+        </is>
+      </c>
+      <c r="C184" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/performance-and-statistics</t>
+        </is>
+      </c>
+      <c r="D184" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/rendement-et-statistiques</t>
+        </is>
+      </c>
+      <c r="E184" s="1" t="inlineStr">
+        <is>
+          <t>Tuesday, July 4, 2023</t>
+        </is>
+      </c>
+      <c r="F184" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G184" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H184" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I184" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J184" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K184" s="1" t="inlineStr"/>
+      <c r="L184" s="1" t="n">
+        <v>607</v>
+      </c>
+      <c r="M184" s="1" t="n">
+        <v>790</v>
+      </c>
+      <c r="N184" s="1" t="n">
+        <v>697</v>
+      </c>
+      <c r="O184" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P184" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="1" t="n">
+        <v>100004</v>
+      </c>
+      <c r="B185" s="1" t="inlineStr">
+        <is>
+          <t>Contact us</t>
+        </is>
+      </c>
+      <c r="C185" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/contact-us</t>
+        </is>
+      </c>
+      <c r="D185" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/contactez-nous</t>
+        </is>
+      </c>
+      <c r="E185" s="1" t="inlineStr">
+        <is>
+          <t>Wednesday, May 14, 2025</t>
+        </is>
+      </c>
+      <c r="F185" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G185" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H185" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I185" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J185" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K185" s="1" t="inlineStr"/>
+      <c r="L185" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="M185" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="N185" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="O185" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P185" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="1" t="n">
+        <v>572336</v>
+      </c>
+      <c r="B186" s="1" t="inlineStr">
+        <is>
+          <t>Quarterly Financial Report For the quarter ended December 31, 2023</t>
+        </is>
+      </c>
+      <c r="C186" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/publication/quarterly-financial-report-quarter-ended-december-31-2023</t>
+        </is>
+      </c>
+      <c r="D186" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/publication/rapport-financier-trimestriel-pour-trimestre-termine-31-decembre-2023</t>
+        </is>
+      </c>
+      <c r="E186" s="1" t="inlineStr">
+        <is>
+          <t>Thursday, February 29, 2024</t>
+        </is>
+      </c>
+      <c r="F186" s="1" t="n">
+        <v>2024</v>
+      </c>
+      <c r="G186" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H186" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I186" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J186" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K186" s="1" t="inlineStr"/>
+      <c r="L186" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="M186" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="N186" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="O186" s="1" t="inlineStr">
+        <is>
+          <t>Publication</t>
+        </is>
+      </c>
+      <c r="P186" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="n">
+        <v>571891</v>
+      </c>
+      <c r="B187" s="1" t="inlineStr">
+        <is>
+          <t>Quarterly Financial Report for the quarter ended June 30, 2023</t>
+        </is>
+      </c>
+      <c r="C187" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/publication/quarterly-financial-report-quarter-ended-june-30-2023</t>
+        </is>
+      </c>
+      <c r="D187" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/publication/rapport-financier-trimestriel-pour-trimestre-termine-30-juin-2023</t>
+        </is>
+      </c>
+      <c r="E187" s="1" t="inlineStr">
+        <is>
+          <t>Wednesday, August 30, 2023</t>
+        </is>
+      </c>
+      <c r="F187" s="1" t="n">
+        <v>2024</v>
+      </c>
+      <c r="G187" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H187" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I187" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J187" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K187" s="1" t="inlineStr"/>
+      <c r="L187" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="M187" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="N187" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="O187" s="1" t="inlineStr">
+        <is>
+          <t>Publication</t>
+        </is>
+      </c>
+      <c r="P187" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="n">
+        <v>571315</v>
+      </c>
+      <c r="B188" s="1" t="inlineStr">
+        <is>
+          <t>Quarterly Financial Report For the quarter ended December 31, 2022</t>
+        </is>
+      </c>
+      <c r="C188" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/publication/quarterly-financial-report-quarter-ended-december-31-2022</t>
+        </is>
+      </c>
+      <c r="D188" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/publication/rapport-financier-trimestriel-pour-trimestre-termine-31-decembre-2022</t>
+        </is>
+      </c>
+      <c r="E188" s="1" t="inlineStr">
+        <is>
+          <t>Wednesday, March 1, 2023</t>
+        </is>
+      </c>
+      <c r="F188" s="1" t="n">
+        <v>2024</v>
+      </c>
+      <c r="G188" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H188" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I188" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J188" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K188" s="1" t="inlineStr"/>
+      <c r="L188" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="M188" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="N188" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="O188" s="1" t="inlineStr">
+        <is>
+          <t>Publication</t>
+        </is>
+      </c>
+      <c r="P188" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="n">
+        <v>571043</v>
+      </c>
+      <c r="B189" s="1" t="inlineStr">
+        <is>
+          <t>Quarterly Financial Report For the quarter ended September 30, 2022</t>
+        </is>
+      </c>
+      <c r="C189" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/publication/quarterly-financial-report-quarter-ended-september-30-2022</t>
+        </is>
+      </c>
+      <c r="D189" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/publication/rapport-financier-trimestriel-pour-trimestre-termine-30-septembre-2022</t>
+        </is>
+      </c>
+      <c r="E189" s="1" t="inlineStr">
+        <is>
+          <t>Friday, November 25, 2022</t>
+        </is>
+      </c>
+      <c r="F189" s="1" t="n">
+        <v>2024</v>
+      </c>
+      <c r="G189" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H189" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I189" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J189" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K189" s="1" t="inlineStr"/>
+      <c r="L189" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="M189" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="N189" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="O189" s="1" t="inlineStr">
+        <is>
+          <t>Publication</t>
+        </is>
+      </c>
+      <c r="P189" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="1" t="n">
+        <v>572734</v>
+      </c>
+      <c r="B190" s="1" t="inlineStr">
+        <is>
+          <t>Air travel complaints per 100 flights – by airline – July 2023 to September 2024</t>
+        </is>
+      </c>
+      <c r="C190" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/air-travel-complaints-100-flights-airline-july-2023-september-2024</t>
+        </is>
+      </c>
+      <c r="D190" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/nombre-plaintes-aeriennes-par-100-vols-par-compagnie-aerienne-juillet-2023-a-septembre-2024</t>
+        </is>
+      </c>
+      <c r="E190" s="1" t="inlineStr">
+        <is>
+          <t>Wednesday, October 30, 2024</t>
+        </is>
+      </c>
+      <c r="F190" s="1" t="n">
+        <v>2024</v>
+      </c>
+      <c r="G190" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H190" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I190" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J190" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K190" s="1" t="inlineStr"/>
+      <c r="L190" s="1" t="n">
+        <v>52</v>
+      </c>
+      <c r="M190" s="1" t="n">
+        <v>67</v>
+      </c>
+      <c r="N190" s="1" t="n">
+        <v>64</v>
+      </c>
+      <c r="O190" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P190" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="1" t="n">
+        <v>572431</v>
+      </c>
+      <c r="B191" s="1" t="inlineStr">
+        <is>
+          <t>Air travel complaints per 100 flights – by airline – January 2023 to March 2024</t>
+        </is>
+      </c>
+      <c r="C191" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/air-travel-complaints-100-flights-airline-january-2023-march-2024</t>
+        </is>
+      </c>
+      <c r="D191" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/nombre-plaintes-aeriennes-par-100-vols-par-compagnie-aerienne-janvier-2023-a-mars-2024</t>
+        </is>
+      </c>
+      <c r="E191" s="1" t="inlineStr">
+        <is>
+          <t>Tuesday, April 30, 2024</t>
+        </is>
+      </c>
+      <c r="F191" s="1" t="n">
+        <v>2024</v>
+      </c>
+      <c r="G191" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H191" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I191" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J191" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K191" s="1" t="inlineStr"/>
+      <c r="L191" s="1" t="n">
+        <v>119</v>
+      </c>
+      <c r="M191" s="1" t="n">
+        <v>158</v>
+      </c>
+      <c r="N191" s="1" t="n">
+        <v>141</v>
+      </c>
+      <c r="O191" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P191" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="1" t="n">
+        <v>572279</v>
+      </c>
+      <c r="B192" s="1" t="inlineStr">
+        <is>
+          <t>Air travel complaints per 100 flights – by airline – October 2022 to December 2023</t>
+        </is>
+      </c>
+      <c r="C192" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/air-travel-complaints-100-flights-airline-october-2022-december-2023</t>
+        </is>
+      </c>
+      <c r="D192" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/nombre-plaintes-aeriennes-par-100-vols-par-compagnie-aerienne-octobre-2022-a-decembre-2023</t>
+        </is>
+      </c>
+      <c r="E192" s="1" t="inlineStr">
+        <is>
+          <t>Thursday, February 1, 2024</t>
+        </is>
+      </c>
+      <c r="F192" s="1" t="n">
+        <v>2024</v>
+      </c>
+      <c r="G192" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H192" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I192" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J192" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K192" s="1" t="inlineStr"/>
+      <c r="L192" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="M192" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="N192" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="O192" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P192" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="1" t="n">
+        <v>567802</v>
+      </c>
+      <c r="B193" s="1" t="inlineStr">
+        <is>
+          <t>Inquiries</t>
+        </is>
+      </c>
+      <c r="C193" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/inquiries</t>
+        </is>
+      </c>
+      <c r="D193" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/enquetes</t>
+        </is>
+      </c>
+      <c r="E193" s="1" t="inlineStr">
+        <is>
+          <t>Monday, April 30, 2018</t>
+        </is>
+      </c>
+      <c r="F193" s="1" t="n">
+        <v>2024</v>
+      </c>
+      <c r="G193" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H193" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I193" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J193" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K193" s="1" t="inlineStr"/>
+      <c r="L193" s="1" t="n">
+        <v>150</v>
+      </c>
+      <c r="M193" s="1" t="n">
+        <v>189</v>
+      </c>
+      <c r="N193" s="1" t="n">
+        <v>174</v>
+      </c>
+      <c r="O193" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P193" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="1" t="n">
+        <v>567862</v>
+      </c>
+      <c r="B194" s="1" t="inlineStr">
+        <is>
+          <t>Air passenger protection regulations – Have your say!</t>
+        </is>
+      </c>
+      <c r="C194" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/content/air-passenger-protection-regulations-have-your-say</t>
+        </is>
+      </c>
+      <c r="D194" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/content/reglement-sur-protection-des-voyageurs-aeriens-exprimez-vous</t>
+        </is>
+      </c>
+      <c r="E194" s="1" t="inlineStr">
+        <is>
+          <t>Monday, May 28, 2018</t>
+        </is>
+      </c>
+      <c r="F194" s="1" t="n">
+        <v>2023</v>
+      </c>
+      <c r="G194" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H194" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I194" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J194" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K194" s="1" t="inlineStr"/>
+      <c r="L194" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="M194" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="N194" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="O194" s="1" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="P194" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="1" t="n">
+        <v>570500</v>
+      </c>
+      <c r="B195" s="1" t="inlineStr">
+        <is>
+          <t>Supplementary Guidance: Evidentiary Requirement for Airlines for Complaints Relating to Crew Shortages</t>
+        </is>
+      </c>
+      <c r="C195" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/publication/supplementary-guidance-evidentiary-requirement-airlines-complaints-relating-crew</t>
+        </is>
+      </c>
+      <c r="D195" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/publication/guide-complementaire-preuves-exigees-des-compagnies-aeriennes-faisant-lobjet-plaintes</t>
+        </is>
+      </c>
+      <c r="E195" s="1" t="inlineStr">
+        <is>
+          <t>Friday, February 11, 2022</t>
+        </is>
+      </c>
+      <c r="F195" s="1" t="n">
+        <v>2023</v>
+      </c>
+      <c r="G195" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H195" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I195" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J195" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K195" s="1" t="inlineStr"/>
+      <c r="L195" s="1" t="n">
+        <v>320</v>
+      </c>
+      <c r="M195" s="1" t="n">
+        <v>391</v>
+      </c>
+      <c r="N195" s="1" t="n">
+        <v>399</v>
+      </c>
+      <c r="O195" s="1" t="inlineStr">
+        <is>
+          <t>Publication</t>
+        </is>
+      </c>
+      <c r="P195" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="1" t="n">
+        <v>568481</v>
+      </c>
+      <c r="B196" s="1" t="inlineStr">
+        <is>
+          <t>Quarterly Financial Report for the quarter ended December 31, 2018</t>
+        </is>
+      </c>
+      <c r="C196" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/publication/quarterly-financial-report-quarter-ended-december-31-2018</t>
+        </is>
+      </c>
+      <c r="D196" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/publication/rapport-financier-trimestriel-pour-trimestre-termine-31-decembre-2018</t>
+        </is>
+      </c>
+      <c r="E196" s="1" t="inlineStr">
+        <is>
+          <t>Thursday, February 28, 2019</t>
+        </is>
+      </c>
+      <c r="F196" s="1" t="n">
+        <v>2023</v>
+      </c>
+      <c r="G196" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H196" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I196" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J196" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K196" s="1" t="inlineStr"/>
+      <c r="L196" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="M196" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="N196" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="O196" s="1" t="inlineStr">
+        <is>
+          <t>Publication</t>
+        </is>
+      </c>
+      <c r="P196" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="1" t="n">
+        <v>568309</v>
+      </c>
+      <c r="B197" s="1" t="inlineStr">
+        <is>
+          <t>Quarterly Financial Report for the quarter ended September 30, 2018</t>
+        </is>
+      </c>
+      <c r="C197" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/publication/quarterly-financial-report-quarter-ended-september-30-2018</t>
+        </is>
+      </c>
+      <c r="D197" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/publication/rapport-financier-trimestriel-pour-trimestre-termine-30-septembre-2018</t>
+        </is>
+      </c>
+      <c r="E197" s="1" t="inlineStr">
+        <is>
+          <t>Friday, November 30, 2018</t>
+        </is>
+      </c>
+      <c r="F197" s="1" t="n">
+        <v>2023</v>
+      </c>
+      <c r="G197" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H197" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I197" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J197" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K197" s="1" t="inlineStr"/>
+      <c r="L197" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="M197" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="N197" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="O197" s="1" t="inlineStr">
+        <is>
+          <t>Publication</t>
+        </is>
+      </c>
+      <c r="P197" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="1" t="n">
+        <v>568117</v>
+      </c>
+      <c r="B198" s="1" t="inlineStr">
+        <is>
+          <t>Quarterly Financial Report for the quarter ended June 30, 2018</t>
+        </is>
+      </c>
+      <c r="C198" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/publication/quarterly-financial-report-quarter-ended-june-30-2018</t>
+        </is>
+      </c>
+      <c r="D198" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/publication/rapport-financier-trimestriel-pour-trimestre-termine-30-juin-2018</t>
+        </is>
+      </c>
+      <c r="E198" s="1" t="inlineStr">
+        <is>
+          <t>Thursday, August 30, 2018</t>
+        </is>
+      </c>
+      <c r="F198" s="1" t="n">
+        <v>2023</v>
+      </c>
+      <c r="G198" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H198" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I198" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J198" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K198" s="1" t="inlineStr"/>
+      <c r="L198" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="M198" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="N198" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="O198" s="1" t="inlineStr">
+        <is>
+          <t>Publication</t>
+        </is>
+      </c>
+      <c r="P198" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="1" t="n">
+        <v>567667</v>
+      </c>
+      <c r="B199" s="1" t="inlineStr">
+        <is>
+          <t>Quarterly Financial Report for the quarter ended December 31, 2017</t>
+        </is>
+      </c>
+      <c r="C199" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/publication/quarterly-financial-report-quarter-ended-december-31-2017</t>
+        </is>
+      </c>
+      <c r="D199" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/publication/rapport-financier-trimestriel-pour-trimestre-termine-31-decembre-2017</t>
+        </is>
+      </c>
+      <c r="E199" s="1" t="inlineStr">
+        <is>
+          <t>Tuesday, February 27, 2018</t>
+        </is>
+      </c>
+      <c r="F199" s="1" t="n">
+        <v>2023</v>
+      </c>
+      <c r="G199" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H199" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I199" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J199" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K199" s="1" t="inlineStr"/>
+      <c r="L199" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="M199" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="N199" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="O199" s="1" t="inlineStr">
+        <is>
+          <t>Publication</t>
+        </is>
+      </c>
+      <c r="P199" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="1" t="n">
+        <v>571623</v>
+      </c>
+      <c r="B200" s="1" t="inlineStr">
+        <is>
+          <t>Opening Remarks from Tom Oommen, DG Analysis and Outreach, to the Standing Committee on Transport, Infrastructure and Communities – November 28, 2022</t>
+        </is>
+      </c>
+      <c r="C200" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/content/opening-remarks-tom-oommen-dg-analysis-and-outreach-standing-committee-transport</t>
+        </is>
+      </c>
+      <c r="D200" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/contenu/allocution-douverture-tom-oommen-directeur-general-analyse-et-liaison-otc-a-lintention</t>
+        </is>
+      </c>
+      <c r="E200" s="1" t="inlineStr">
+        <is>
+          <t>Monday, November 28, 2022</t>
+        </is>
+      </c>
+      <c r="F200" s="1" t="n">
+        <v>2023</v>
+      </c>
+      <c r="G200" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H200" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I200" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J200" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K200" s="1" t="inlineStr"/>
+      <c r="L200" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="M200" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="N200" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="O200" s="1" t="inlineStr">
+        <is>
+          <t>Speeches</t>
+        </is>
+      </c>
+      <c r="P200" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="1" t="n">
+        <v>571835</v>
+      </c>
+      <c r="B201" s="1" t="inlineStr">
+        <is>
+          <t>Air travel complaints per 100 flights, by airline, April 2022 to June 2023</t>
+        </is>
+      </c>
+      <c r="C201" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/air-travel-complaints-100-flights-airline-april-2022-june-2023</t>
+        </is>
+      </c>
+      <c r="D201" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/nombre-plaintes-aeriennes-par-100-vols-par-compagnie-aerienne-avril-2022-a-juin-2023</t>
+        </is>
+      </c>
+      <c r="E201" s="1" t="inlineStr">
+        <is>
+          <t>Tuesday, November 7, 2023</t>
+        </is>
+      </c>
+      <c r="F201" s="1" t="n">
+        <v>2023</v>
+      </c>
+      <c r="G201" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H201" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I201" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J201" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K201" s="1" t="inlineStr"/>
+      <c r="L201" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="M201" s="1" t="n">
+        <v>72</v>
+      </c>
+      <c r="N201" s="1" t="n">
+        <v>67</v>
+      </c>
+      <c r="O201" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P201" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="1" t="n">
+        <v>566805</v>
+      </c>
+      <c r="B202" s="1" t="inlineStr">
+        <is>
+          <t>Forms for adjudication</t>
+        </is>
+      </c>
+      <c r="C202" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/forms-adjudication</t>
+        </is>
+      </c>
+      <c r="D202" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/formulaires-lies-au-reglement-des-differends</t>
+        </is>
+      </c>
+      <c r="E202" s="1" t="inlineStr">
+        <is>
+          <t>Friday, August 30, 2019</t>
+        </is>
+      </c>
+      <c r="F202" s="1" t="n">
+        <v>2023</v>
+      </c>
+      <c r="G202" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H202" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I202" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J202" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K202" s="1" t="inlineStr"/>
+      <c r="L202" s="1" t="n">
+        <v>137</v>
+      </c>
+      <c r="M202" s="1" t="n">
+        <v>180</v>
+      </c>
+      <c r="N202" s="1" t="n">
+        <v>170</v>
+      </c>
+      <c r="O202" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P202" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="1" t="n">
+        <v>566806</v>
+      </c>
+      <c r="B203" s="1" t="inlineStr">
+        <is>
+          <t>How to manage your adjudication case</t>
+        </is>
+      </c>
+      <c r="C203" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/how-manage-your-adjudication-case</t>
+        </is>
+      </c>
+      <c r="D203" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/comment-gerer-votre-cas-reglement-des-differends</t>
+        </is>
+      </c>
+      <c r="E203" s="1" t="inlineStr">
+        <is>
+          <t>Friday, August 26, 2016</t>
+        </is>
+      </c>
+      <c r="F203" s="1" t="n">
+        <v>2023</v>
+      </c>
+      <c r="G203" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H203" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I203" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J203" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K203" s="1" t="inlineStr"/>
+      <c r="L203" s="1" t="n">
+        <v>86</v>
+      </c>
+      <c r="M203" s="1" t="n">
+        <v>118</v>
+      </c>
+      <c r="N203" s="1" t="n">
+        <v>111</v>
+      </c>
+      <c r="O203" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P203" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="1" t="n">
+        <v>566841</v>
+      </c>
+      <c r="B204" s="1" t="inlineStr">
+        <is>
+          <t>Provincial and territorial government authorities (dealing with consumer matters including travel)</t>
+        </is>
+      </c>
+      <c r="C204" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/provincial-and-territorial-government-authorities-dealing-with-consumer-matters-including-travel</t>
+        </is>
+      </c>
+      <c r="D204" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/instances-gouvernementales-provinciales-et-territoriales-traitant-des-questions-touchant</t>
+        </is>
+      </c>
+      <c r="E204" s="1" t="inlineStr">
+        <is>
+          <t>Monday, March 27, 2023</t>
+        </is>
+      </c>
+      <c r="F204" s="1" t="n">
+        <v>2023</v>
+      </c>
+      <c r="G204" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H204" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I204" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J204" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K204" s="1" t="inlineStr"/>
+      <c r="L204" s="1" t="n">
+        <v>248</v>
+      </c>
+      <c r="M204" s="1" t="n">
+        <v>340</v>
+      </c>
+      <c r="N204" s="1" t="n">
+        <v>327</v>
+      </c>
+      <c r="O204" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P204" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="1" t="n">
+        <v>92887</v>
+      </c>
+      <c r="B205" s="1" t="inlineStr">
+        <is>
+          <t>News feeds</t>
+        </is>
+      </c>
+      <c r="C205" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/news-feeds</t>
+        </is>
+      </c>
+      <c r="D205" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/fils-nouvelles</t>
+        </is>
+      </c>
+      <c r="E205" s="1" t="inlineStr">
+        <is>
+          <t>Wednesday, June 7, 2023</t>
+        </is>
+      </c>
+      <c r="F205" s="1" t="n">
+        <v>2023</v>
+      </c>
+      <c r="G205" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H205" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I205" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J205" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K205" s="1" t="inlineStr"/>
+      <c r="L205" s="1" t="n">
+        <v>432</v>
+      </c>
+      <c r="M205" s="1" t="n">
+        <v>522</v>
+      </c>
+      <c r="N205" s="1" t="n">
+        <v>466</v>
+      </c>
+      <c r="O205" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P205" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="1" t="n">
+        <v>567640</v>
+      </c>
+      <c r="B206" s="1" t="inlineStr">
+        <is>
+          <t>Memorandum of Understanding between the Canadian Transportation Agency and the Secretariat of Communications and Transports of the United Mexican States concerning Engagement and Information Sharing</t>
+        </is>
+      </c>
+      <c r="C206" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/mou-between-cta-and-secretariat-communications-transport-united-mexican-states-concerning-engagement-information-sharing</t>
+        </is>
+      </c>
+      <c r="D206" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/protocole-dentente-entre-lotc-et-le-secretaire-des-communications-et-des-transports-des-etats-unis-du-mexique-concernant-lengagement-et-le-partage-de-linformation</t>
+        </is>
+      </c>
+      <c r="E206" s="1" t="inlineStr">
+        <is>
+          <t>Monday, February 12, 2018</t>
+        </is>
+      </c>
+      <c r="F206" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="G206" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H206" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I206" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J206" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K206" s="1" t="inlineStr"/>
+      <c r="L206" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="M206" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="N206" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="O206" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P206" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="1" t="n">
+        <v>567160</v>
+      </c>
+      <c r="B207" s="1" t="inlineStr">
+        <is>
+          <t>How to File a Settlement Agreement</t>
+        </is>
+      </c>
+      <c r="C207" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/how-file-a-settlement-agreement</t>
+        </is>
+      </c>
+      <c r="D207" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/comment-deposer-un-reglement-extrajudiciaire</t>
+        </is>
+      </c>
+      <c r="E207" s="1" t="inlineStr">
+        <is>
+          <t>Thursday, July 6, 2017</t>
+        </is>
+      </c>
+      <c r="F207" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="G207" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H207" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I207" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J207" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K207" s="1" t="inlineStr"/>
+      <c r="L207" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="M207" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="N207" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="O207" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P207" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="1" t="n">
+        <v>566810</v>
+      </c>
+      <c r="B208" s="1" t="inlineStr">
+        <is>
+          <t>Disputes about the transfer and discontinuance of railway lines</t>
+        </is>
+      </c>
+      <c r="C208" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/disputes-about-transfer-and-discontinuance-railway-lines</t>
+        </is>
+      </c>
+      <c r="D208" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/differends-sur-transfert-et-cessation-dexploitation-lignes-chemin-fer</t>
+        </is>
+      </c>
+      <c r="E208" s="1" t="inlineStr">
+        <is>
+          <t>Tuesday, June 21, 2016</t>
+        </is>
+      </c>
+      <c r="F208" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="G208" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H208" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I208" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J208" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K208" s="1" t="inlineStr"/>
+      <c r="L208" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="M208" s="1" t="n">
+        <v>43</v>
+      </c>
+      <c r="N208" s="1" t="n">
+        <v>42</v>
+      </c>
+      <c r="O208" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P208" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="1" t="n">
+        <v>566812</v>
+      </c>
+      <c r="B209" s="1" t="inlineStr">
+        <is>
+          <t>Issues eligible for level of service arbitration</t>
+        </is>
+      </c>
+      <c r="C209" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/issues-eligible-level-service-arbitration</t>
+        </is>
+      </c>
+      <c r="D209" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/questions-admissibles-pour-larbitrage-portant-sur-niveau-service</t>
+        </is>
+      </c>
+      <c r="E209" s="1" t="inlineStr">
+        <is>
+          <t>Monday, May 28, 2018</t>
+        </is>
+      </c>
+      <c r="F209" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="G209" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H209" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I209" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J209" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K209" s="1" t="inlineStr"/>
+      <c r="L209" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="M209" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="N209" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="O209" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P209" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="1" t="n">
+        <v>566820</v>
+      </c>
+      <c r="B210" s="1" t="inlineStr">
+        <is>
+          <t>Memorandum of Understanding</t>
+        </is>
+      </c>
+      <c r="C210" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/memorandum-understanding</t>
+        </is>
+      </c>
+      <c r="D210" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/protocole-dentente</t>
+        </is>
+      </c>
+      <c r="E210" s="1" t="inlineStr">
+        <is>
+          <t>Thursday, October 22, 2015</t>
+        </is>
+      </c>
+      <c r="F210" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="G210" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H210" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I210" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J210" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K210" s="1" t="inlineStr"/>
+      <c r="L210" s="1" t="n">
+        <v>65</v>
+      </c>
+      <c r="M210" s="1" t="n">
+        <v>74</v>
+      </c>
+      <c r="N210" s="1" t="n">
+        <v>83</v>
+      </c>
+      <c r="O210" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P210" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="1" t="n">
+        <v>566828</v>
+      </c>
+      <c r="B211" s="1" t="inlineStr">
+        <is>
+          <t>How to file a position statement or a request to intervene</t>
+        </is>
+      </c>
+      <c r="C211" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/how-file-a-position-statement-or-a-request-intervene</t>
+        </is>
+      </c>
+      <c r="D211" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/comment-deposer-un-enonce-position-ou-une-requete-dintervention</t>
+        </is>
+      </c>
+      <c r="E211" s="1" t="inlineStr">
+        <is>
+          <t>Tuesday, October 20, 2015</t>
+        </is>
+      </c>
+      <c r="F211" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="G211" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H211" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I211" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J211" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K211" s="1" t="inlineStr"/>
+      <c r="L211" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="M211" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="N211" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="O211" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P211" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="1" t="n">
+        <v>418828</v>
+      </c>
+      <c r="B212" s="1" t="inlineStr">
+        <is>
+          <t>Personal Information Collection Statement</t>
+        </is>
+      </c>
+      <c r="C212" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/personal-information-collection-statement</t>
+        </is>
+      </c>
+      <c r="D212" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/enonce-collecte-renseignements-personnels</t>
+        </is>
+      </c>
+      <c r="E212" s="1" t="inlineStr">
+        <is>
+          <t>Thursday, April 7, 2016</t>
+        </is>
+      </c>
+      <c r="F212" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="G212" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H212" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I212" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J212" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K212" s="1" t="inlineStr"/>
+      <c r="L212" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="M212" s="1" t="n">
+        <v>46</v>
+      </c>
+      <c r="N212" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="O212" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P212" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="1" t="n">
+        <v>418130</v>
+      </c>
+      <c r="B213" s="1" t="inlineStr">
+        <is>
+          <t>Rail noise and vibration: Requirements for railway companies</t>
+        </is>
+      </c>
+      <c r="C213" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/rail-noise-and-vibration-requirements-railway-companies</t>
+        </is>
+      </c>
+      <c r="D213" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/bruit-et-vibrations-ferroviaires-exigences-pour-compagnies-chemin-fer</t>
+        </is>
+      </c>
+      <c r="E213" s="1" t="inlineStr">
+        <is>
+          <t>Tuesday, July 30, 2019</t>
+        </is>
+      </c>
+      <c r="F213" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="G213" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H213" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I213" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J213" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K213" s="1" t="inlineStr"/>
+      <c r="L213" s="1" t="n">
+        <v>262</v>
+      </c>
+      <c r="M213" s="1" t="n">
+        <v>324</v>
+      </c>
+      <c r="N213" s="1" t="n">
+        <v>316</v>
+      </c>
+      <c r="O213" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P213" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="1" t="n">
+        <v>569157</v>
+      </c>
+      <c r="B214" s="1" t="inlineStr">
+        <is>
+          <t>Canadian Transportation Agency issues temporary exemptions to certain Air Passenger Protection Regulations provisions to address the COVID-19 pandemic</t>
+        </is>
+      </c>
+      <c r="C214" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/content/canadian-transportation-agency-issues-temporary-exemptions-certain-air-passenger-protection</t>
+        </is>
+      </c>
+      <c r="D214" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/content/loffice-des-transports-canada-accorde-des-derogations-temporaires-a-certaines-dispositions</t>
+        </is>
+      </c>
+      <c r="E214" s="1" t="inlineStr">
+        <is>
+          <t>Friday, March 13, 2020</t>
+        </is>
+      </c>
+      <c r="F214" s="1" t="n">
+        <v>2021</v>
+      </c>
+      <c r="G214" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H214" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I214" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J214" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K214" s="1" t="inlineStr"/>
+      <c r="L214" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="M214" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="N214" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="O214" s="1" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="P214" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="1" t="n">
+        <v>568732</v>
+      </c>
+      <c r="B215" s="1" t="inlineStr">
+        <is>
+          <t>Accessible Transportation for Persons with Disabilities Regulations now finalized</t>
+        </is>
+      </c>
+      <c r="C215" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/content/accessible-transportation-persons-with-disabilities-regulations-now-finalized</t>
+        </is>
+      </c>
+      <c r="D215" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/content/reglement-sur-transports-accessibles-aux-personnes-handicapees-est-maintenant-finalise</t>
+        </is>
+      </c>
+      <c r="E215" s="1" t="inlineStr">
+        <is>
+          <t>Wednesday, July 10, 2019</t>
+        </is>
+      </c>
+      <c r="F215" s="1" t="n">
+        <v>2021</v>
+      </c>
+      <c r="G215" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H215" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I215" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J215" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K215" s="1" t="inlineStr"/>
+      <c r="L215" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="M215" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="N215" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="O215" s="1" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="P215" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="1" t="n">
+        <v>568349</v>
+      </c>
+      <c r="B216" s="1" t="inlineStr">
+        <is>
+          <t>Proposed Air Passenger Protection Regulations to be published in Part I of the Canada Gazette</t>
+        </is>
+      </c>
+      <c r="C216" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/content/proposed-air-passenger-protection-regulations-be-published-part-i-canada-gazette</t>
+        </is>
+      </c>
+      <c r="D216" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/content/publication-projet-reglement-sur-protection-des-passagers-aeriens-dans-partie-i-gazette</t>
+        </is>
+      </c>
+      <c r="E216" s="1" t="inlineStr">
+        <is>
+          <t>Monday, December 17, 2018</t>
+        </is>
+      </c>
+      <c r="F216" s="1" t="n">
+        <v>2021</v>
+      </c>
+      <c r="G216" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H216" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I216" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J216" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K216" s="1" t="inlineStr"/>
+      <c r="L216" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="M216" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="N216" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="O216" s="1" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="P216" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="1" t="n">
+        <v>567872</v>
+      </c>
+      <c r="B217" s="1" t="inlineStr">
+        <is>
+          <t>Canadian Transportation Agency Launches Consultation on Rail Transportation</t>
+        </is>
+      </c>
+      <c r="C217" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/content/canadian-transportation-agency-launches-consultation-rail-transportation</t>
+        </is>
+      </c>
+      <c r="D217" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/content/loffice-des-transports-canada-lance-une-consultation-sur-transport-ferroviaire</t>
+        </is>
+      </c>
+      <c r="E217" s="1" t="inlineStr">
+        <is>
+          <t>Thursday, May 31, 2018</t>
+        </is>
+      </c>
+      <c r="F217" s="1" t="n">
+        <v>2021</v>
+      </c>
+      <c r="G217" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H217" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I217" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J217" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K217" s="1" t="inlineStr"/>
+      <c r="L217" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="M217" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="N217" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="O217" s="1" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="P217" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="1" t="n">
+        <v>567639</v>
+      </c>
+      <c r="B218" s="1" t="inlineStr">
+        <is>
+          <t>Canadian Transportation Agency and Rail Transport Regulatory Agency sign MOU on information sharing</t>
+        </is>
+      </c>
+      <c r="C218" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/content/canadian-transportation-agency-and-rail-transport-regulatory-agency-sign-mou-information</t>
+        </is>
+      </c>
+      <c r="D218" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/content/loffice-des-transports-canada-et-lorganisme-reglementation-transport-ferroviaire-signe-un</t>
+        </is>
+      </c>
+      <c r="E218" s="1" t="inlineStr">
+        <is>
+          <t>Monday, February 12, 2018</t>
+        </is>
+      </c>
+      <c r="F218" s="1" t="n">
+        <v>2021</v>
+      </c>
+      <c r="G218" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H218" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I218" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J218" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K218" s="1" t="inlineStr"/>
+      <c r="L218" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="M218" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="N218" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="O218" s="1" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="P218" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="1" t="n">
+        <v>129300</v>
+      </c>
+      <c r="B219" s="1" t="inlineStr">
+        <is>
+          <t>Travelling</t>
+        </is>
+      </c>
+      <c r="C219" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/travelling</t>
+        </is>
+      </c>
+      <c r="D219" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/voyager</t>
+        </is>
+      </c>
+      <c r="E219" s="1" t="inlineStr">
+        <is>
+          <t>Thursday, March 31, 2016</t>
+        </is>
+      </c>
+      <c r="F219" s="1" t="n">
+        <v>2021</v>
+      </c>
+      <c r="G219" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H219" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I219" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J219" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K219" s="1" t="inlineStr"/>
+      <c r="L219" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="M219" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="N219" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="O219" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P219" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="1" t="n">
+        <v>569786</v>
+      </c>
+      <c r="B220" s="1" t="inlineStr">
+        <is>
+          <t>CTA launches consultation on new refund requirements</t>
+        </is>
+      </c>
+      <c r="C220" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/content/cta-launches-consultation-new-refund-requirements</t>
+        </is>
+      </c>
+      <c r="D220" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/content/lotc-lance-une-consultation-sur-nouvelles-exigences-remboursement</t>
+        </is>
+      </c>
+      <c r="E220" s="1" t="inlineStr">
+        <is>
+          <t>Monday, December 21, 2020</t>
+        </is>
+      </c>
+      <c r="F220" s="1" t="n">
+        <v>2020</v>
+      </c>
+      <c r="G220" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H220" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I220" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J220" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K220" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L220" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="M220" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="N220" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="O220" s="1" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="P220" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="1" t="n">
+        <v>569737</v>
+      </c>
+      <c r="B221" s="1" t="inlineStr">
+        <is>
+          <t>CTA Launches Consultation on Accessible Transportation Guidelines for Medium and Small Transportation Service Providers</t>
+        </is>
+      </c>
+      <c r="C221" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/content/cta-launches-consultation-accessible-transportation-guidelines-medium-and-small</t>
+        </is>
+      </c>
+      <c r="D221" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/content/lotc-lance-une-consultation-sur-lignes-directrices-relatives-aux-transports-accessibles-a</t>
+        </is>
+      </c>
+      <c r="E221" s="1" t="inlineStr">
+        <is>
+          <t>Thursday, December 3, 2020</t>
+        </is>
+      </c>
+      <c r="F221" s="1" t="n">
+        <v>2020</v>
+      </c>
+      <c r="G221" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H221" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I221" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J221" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K221" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L221" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="M221" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="N221" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="O221" s="1" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="P221" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="1" t="n">
+        <v>568571</v>
+      </c>
+      <c r="B222" s="1" t="inlineStr">
+        <is>
+          <t>CTA issues determination on freight rail service issues in the Vancouver area: CN breached its service obligations</t>
+        </is>
+      </c>
+      <c r="C222" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/content/cta-determination-freight-rail-service-issues-vancouver-cn-breached-service-obligations</t>
+        </is>
+      </c>
+      <c r="D222" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/content/otc-determination-problemes-services-transport-ferroviaire-vancouver-cn-manque-obligations-service</t>
+        </is>
+      </c>
+      <c r="E222" s="1" t="inlineStr">
+        <is>
+          <t>Monday, April 15, 2019</t>
+        </is>
+      </c>
+      <c r="F222" s="1" t="n">
+        <v>2020</v>
+      </c>
+      <c r="G222" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H222" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I222" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J222" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K222" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L222" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="M222" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="N222" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="O222" s="1" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="P222" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="1" t="n">
+        <v>569177</v>
+      </c>
+      <c r="B223" s="1" t="inlineStr">
+        <is>
+          <t>COVID-19 and CTA Services</t>
+        </is>
+      </c>
+      <c r="C223" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/covid-19-and-cta-services</t>
+        </is>
+      </c>
+      <c r="D223" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/covid-19-et-services-lotc</t>
+        </is>
+      </c>
+      <c r="E223" s="1" t="inlineStr">
+        <is>
+          <t>Wednesday, March 25, 2020</t>
+        </is>
+      </c>
+      <c r="F223" s="1" t="n">
+        <v>2020</v>
+      </c>
+      <c r="G223" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H223" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I223" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J223" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K223" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L223" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="M223" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="N223" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O223" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P223" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="1" t="n">
+        <v>561608</v>
+      </c>
+      <c r="B224" s="1" t="inlineStr">
+        <is>
+          <t>Personal Information Collection Statement - Adjudication</t>
+        </is>
+      </c>
+      <c r="C224" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/personal-information-collection-statement-adjudication</t>
+        </is>
+      </c>
+      <c r="D224" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/enonce-collecte-renseignements-personnels-processus-decisionnel-formel</t>
+        </is>
+      </c>
+      <c r="E224" s="1" t="inlineStr">
+        <is>
+          <t>Thursday, April 7, 2016</t>
+        </is>
+      </c>
+      <c r="F224" s="1" t="n">
+        <v>2020</v>
+      </c>
+      <c r="G224" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H224" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I224" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J224" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K224" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L224" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="M224" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="N224" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="O224" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P224" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="1" t="n">
+        <v>92951</v>
+      </c>
+      <c r="B225" s="1" t="inlineStr">
+        <is>
+          <t>Organizational chart</t>
+        </is>
+      </c>
+      <c r="C225" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/organizational-chart</t>
+        </is>
+      </c>
+      <c r="D225" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/structure-organisationnelle</t>
+        </is>
+      </c>
+      <c r="E225" s="1" t="inlineStr">
+        <is>
+          <t>Friday, April 1, 2016</t>
+        </is>
+      </c>
+      <c r="F225" s="1" t="n">
+        <v>2020</v>
+      </c>
+      <c r="G225" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H225" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I225" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J225" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K225" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L225" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="M225" s="1" t="n">
+        <v>126</v>
+      </c>
+      <c r="N225" s="1" t="n">
+        <v>127</v>
+      </c>
+      <c r="O225" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P225" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="1" t="n">
+        <v>568749</v>
+      </c>
+      <c r="B226" s="1" t="inlineStr">
+        <is>
+          <t>New Air Passenger Protection Regulations now in force</t>
+        </is>
+      </c>
+      <c r="C226" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/content/new-air-passenger-protection-regulations-now-force</t>
+        </is>
+      </c>
+      <c r="D226" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/content/entree-vigueur-nouveau-reglement-sur-protection-des-passagers-aeriens</t>
+        </is>
+      </c>
+      <c r="E226" s="1" t="inlineStr">
+        <is>
+          <t>Monday, July 15, 2019</t>
+        </is>
+      </c>
+      <c r="F226" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G226" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H226" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I226" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J226" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K226" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L226" s="1" t="n">
+        <v>165</v>
+      </c>
+      <c r="M226" s="1" t="n">
+        <v>186</v>
+      </c>
+      <c r="N226" s="1" t="n">
+        <v>183</v>
+      </c>
+      <c r="O226" s="1" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="P226" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="1" t="n">
+        <v>568738</v>
+      </c>
+      <c r="B227" s="1" t="inlineStr">
+        <is>
+          <t>Rail Transportation Regulations are finalized</t>
+        </is>
+      </c>
+      <c r="C227" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/content/rail-transportation-regulations-are-finalized</t>
+        </is>
+      </c>
+      <c r="D227" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/content/reglement-sur-transport-ferroviaire-est-finalise</t>
+        </is>
+      </c>
+      <c r="E227" s="1" t="inlineStr">
+        <is>
+          <t>Wednesday, July 10, 2019</t>
+        </is>
+      </c>
+      <c r="F227" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G227" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H227" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I227" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J227" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K227" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L227" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="M227" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="N227" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="O227" s="1" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="P227" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="1" t="n">
+        <v>568696</v>
+      </c>
+      <c r="B228" s="1" t="inlineStr">
+        <is>
+          <t>Amended Air Transportation Regulations now finalized</t>
+        </is>
+      </c>
+      <c r="C228" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/content/amended-air-transportation-regulations-now-finalized-0</t>
+        </is>
+      </c>
+      <c r="D228" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/content/reglement-sur-transports-aeriens-modifie-est-maintenant-definitif</t>
+        </is>
+      </c>
+      <c r="E228" s="1" t="inlineStr">
+        <is>
+          <t>Wednesday, June 12, 2019</t>
+        </is>
+      </c>
+      <c r="F228" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G228" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H228" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I228" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J228" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K228" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L228" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="M228" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="N228" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="O228" s="1" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="P228" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="1" t="n">
+        <v>568634</v>
+      </c>
+      <c r="B229" s="1" t="inlineStr">
+        <is>
+          <t>Air Passenger Protection Regulations finalized</t>
+        </is>
+      </c>
+      <c r="C229" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/content/air-passenger-protection-regulations-finalized</t>
+        </is>
+      </c>
+      <c r="D229" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/content/reglement-sur-protection-des-passagers-aeriens-est-finalise</t>
+        </is>
+      </c>
+      <c r="E229" s="1" t="inlineStr">
+        <is>
+          <t>Friday, May 24, 2019</t>
+        </is>
+      </c>
+      <c r="F229" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G229" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H229" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I229" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J229" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K229" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L229" s="1" t="n">
+        <v>2111</v>
+      </c>
+      <c r="M229" s="1" t="n">
+        <v>2252</v>
+      </c>
+      <c r="N229" s="1" t="n">
+        <v>2186</v>
+      </c>
+      <c r="O229" s="1" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="P229" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="1" t="n">
+        <v>568542</v>
+      </c>
+      <c r="B230" s="1" t="inlineStr">
+        <is>
+          <t>Proposed Rail Transportation Regulations published in Part I of the Canada Gazette</t>
+        </is>
+      </c>
+      <c r="C230" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/content/proposed-rail-transportation-regulations-published-part-i-canada-gazette</t>
+        </is>
+      </c>
+      <c r="D230" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/content/publication-projet-reglement-sur-transport-ferroviaire-dans-partie-i-gazette-canada</t>
+        </is>
+      </c>
+      <c r="E230" s="1" t="inlineStr">
+        <is>
+          <t>Monday, April 1, 2019</t>
+        </is>
+      </c>
+      <c r="F230" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G230" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H230" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I230" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J230" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K230" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L230" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="M230" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="N230" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="O230" s="1" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="P230" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="1" t="n">
+        <v>568492</v>
+      </c>
+      <c r="B231" s="1" t="inlineStr">
+        <is>
+          <t>Proposed Accessible Transportation for Persons with Disabilities Regulations now published in Part I of the Canada Gazette</t>
+        </is>
+      </c>
+      <c r="C231" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/content/proposed-accessible-transportation-persons-disabilities-regulations-now-published-canada-gazette</t>
+        </is>
+      </c>
+      <c r="D231" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/content/projet-reglement-transports-accessibles-pour-personnes-handicapees-vient-detre-publie-partie-gazette-canada</t>
+        </is>
+      </c>
+      <c r="E231" s="1" t="inlineStr">
+        <is>
+          <t>Monday, March 11, 2019</t>
+        </is>
+      </c>
+      <c r="F231" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G231" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H231" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I231" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J231" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K231" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L231" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="M231" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="N231" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="O231" s="1" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="P231" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="1" t="n">
+        <v>568395</v>
+      </c>
+      <c r="B232" s="1" t="inlineStr">
+        <is>
+          <t>The Canadian Transportation Agency launches investigation into possible rail service issues in the Vancouver area</t>
+        </is>
+      </c>
+      <c r="C232" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/content/canadian-transportation-agency-launches-investigation-possible-rail-service-issues-vancouver</t>
+        </is>
+      </c>
+      <c r="D232" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/content/loffice-des-transports-canada-lance-une-enquete-sur-des-problemes-possibles-service-de%20service-ferroviaire-Vancouver</t>
+        </is>
+      </c>
+      <c r="E232" s="1" t="inlineStr">
+        <is>
+          <t>Monday, January 14, 2019</t>
+        </is>
+      </c>
+      <c r="F232" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G232" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H232" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I232" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J232" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K232" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L232" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="M232" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="N232" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="O232" s="1" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="P232" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="1" t="n">
+        <v>568747</v>
+      </c>
+      <c r="B233" s="1" t="inlineStr">
+        <is>
+          <t>Entretien du site Web</t>
+        </is>
+      </c>
+      <c r="C233" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/entretien-site-web</t>
+        </is>
+      </c>
+      <c r="D233" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/entretien-site-web</t>
+        </is>
+      </c>
+      <c r="E233" s="1" t="inlineStr">
+        <is>
+          <t>Thursday, July 11, 2019</t>
+        </is>
+      </c>
+      <c r="F233" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G233" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H233" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I233" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J233" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K233" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L233" s="1" t="inlineStr"/>
+      <c r="M233" s="1" t="inlineStr"/>
+      <c r="N233" s="1" t="inlineStr"/>
+      <c r="O233" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P233" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="1" t="n">
+        <v>566803</v>
+      </c>
+      <c r="B234" s="1" t="inlineStr">
+        <is>
+          <t>How to upload files to the secure file transfer system</t>
+        </is>
+      </c>
+      <c r="C234" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/how-upload-files-secure-file-transfer-system</t>
+        </is>
+      </c>
+      <c r="D234" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/comment-telecharger-des-fichiers-vers-un-systeme-transfert-fichiers-securise</t>
+        </is>
+      </c>
+      <c r="E234" s="1" t="inlineStr">
+        <is>
+          <t>Friday, August 26, 2016</t>
+        </is>
+      </c>
+      <c r="F234" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G234" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H234" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I234" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J234" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K234" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L234" s="1" t="n">
+        <v>152</v>
+      </c>
+      <c r="M234" s="1" t="n">
+        <v>173</v>
+      </c>
+      <c r="N234" s="1" t="n">
+        <v>169</v>
+      </c>
+      <c r="O234" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P234" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="1" t="n">
+        <v>561612</v>
+      </c>
+      <c r="B235" s="1" t="inlineStr">
+        <is>
+          <t>Important information related to dispute adjudication</t>
+        </is>
+      </c>
+      <c r="C235" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/important-information-related-dispute-adjudication</t>
+        </is>
+      </c>
+      <c r="D235" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/renseignements-importants-concernant-reglement-formel-des-differends</t>
+        </is>
+      </c>
+      <c r="E235" s="1" t="inlineStr">
+        <is>
+          <t>Wednesday, June 4, 2014</t>
+        </is>
+      </c>
+      <c r="F235" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G235" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H235" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I235" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J235" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K235" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L235" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="M235" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="N235" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="O235" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P235" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="1" t="n">
+        <v>93828</v>
+      </c>
+      <c r="B236" s="1" t="inlineStr">
+        <is>
+          <t>Mandate, tools and values</t>
+        </is>
+      </c>
+      <c r="C236" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/mandate-tools-values</t>
+        </is>
+      </c>
+      <c r="D236" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/mission-mandat</t>
+        </is>
+      </c>
+      <c r="E236" s="1" t="inlineStr">
+        <is>
+          <t>Monday, January 16, 2017</t>
+        </is>
+      </c>
+      <c r="F236" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G236" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H236" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I236" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J236" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K236" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L236" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="M236" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="N236" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="O236" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P236" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="1" t="n">
+        <v>567906</v>
+      </c>
+      <c r="B237" s="1" t="inlineStr">
+        <is>
+          <t>Chair and CEO Scott Streiner addresses The Canadian Automobile Association on June 4, 2018</t>
+        </is>
+      </c>
+      <c r="C237" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/content/chair-and-ceo-scott-streiner-addresses-canadian-automobile-association-june-4-2018</t>
+        </is>
+      </c>
+      <c r="D237" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/contenu/president-et-premier-dirigeant-scott-streiner-prononce-un-discours-a-lassociation-canadienne</t>
+        </is>
+      </c>
+      <c r="E237" s="1" t="inlineStr">
+        <is>
+          <t>Wednesday, June 6, 2018</t>
+        </is>
+      </c>
+      <c r="F237" s="1" t="n">
+        <v>2018</v>
+      </c>
+      <c r="G237" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H237" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I237" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J237" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K237" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L237" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="M237" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="N237" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="O237" s="1" t="inlineStr">
+        <is>
+          <t>Speeches</t>
+        </is>
+      </c>
+      <c r="P237" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="1" t="n">
+        <v>567733</v>
+      </c>
+      <c r="B238" s="1" t="inlineStr">
+        <is>
+          <t>Operating context: conditions affecting our work</t>
+        </is>
+      </c>
+      <c r="C238" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/operating-context-conditions-affecting-our-work</t>
+        </is>
+      </c>
+      <c r="D238" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/contexte-operationnel-conditions-qui-influent-sur-notre-travail</t>
+        </is>
+      </c>
+      <c r="E238" s="1" t="inlineStr">
+        <is>
+          <t>Tuesday, April 3, 2018</t>
+        </is>
+      </c>
+      <c r="F238" s="1" t="n">
+        <v>2018</v>
+      </c>
+      <c r="G238" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H238" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I238" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J238" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K238" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L238" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="M238" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="N238" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="O238" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P238" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="1" t="n">
+        <v>566851</v>
+      </c>
+      <c r="B239" s="1" t="inlineStr">
+        <is>
+          <t>Example complex service</t>
+        </is>
+      </c>
+      <c r="C239" s="1" t="inlineStr"/>
+      <c r="D239" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/service/example-complex-service</t>
+        </is>
+      </c>
+      <c r="E239" s="1" t="inlineStr">
+        <is>
+          <t>Saturday, March 18, 2017</t>
+        </is>
+      </c>
+      <c r="F239" s="1" t="n">
+        <v>2017</v>
+      </c>
+      <c r="G239" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H239" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I239" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J239" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K239" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L239" s="1" t="inlineStr"/>
+      <c r="M239" s="1" t="inlineStr"/>
+      <c r="N239" s="1" t="inlineStr"/>
+      <c r="O239" s="1" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="P239" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="1" t="n">
+        <v>561606</v>
+      </c>
+      <c r="B240" s="1" t="inlineStr">
+        <is>
+          <t>Personal Information Collection Statement - Alternative Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="C240" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/personal-information-collection-statement-alternative-dispute-resolution</t>
+        </is>
+      </c>
+      <c r="D240" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/enonce-collecte-renseignements-personnels-modes-alternatifs-resolution-des-conflits</t>
+        </is>
+      </c>
+      <c r="E240" s="1" t="inlineStr">
+        <is>
+          <t>Tuesday, May 23, 2017</t>
+        </is>
+      </c>
+      <c r="F240" s="1" t="n">
+        <v>2017</v>
+      </c>
+      <c r="G240" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H240" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I240" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J240" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K240" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L240" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="M240" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="N240" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="O240" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P240" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="1" t="n">
+        <v>567049</v>
+      </c>
+      <c r="B241" s="1" t="inlineStr">
+        <is>
+          <t>Enhanced protection of air passengers' rights on the way</t>
+        </is>
+      </c>
+      <c r="C241" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/enhanced-protection-air-passengers-rights-way</t>
+        </is>
+      </c>
+      <c r="D241" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/node/567049</t>
+        </is>
+      </c>
+      <c r="E241" s="1" t="inlineStr">
+        <is>
+          <t>Wednesday, April 26, 2017</t>
+        </is>
+      </c>
+      <c r="F241" s="1" t="n">
+        <v>2017</v>
+      </c>
+      <c r="G241" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H241" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I241" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J241" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K241" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L241" s="1" t="inlineStr"/>
+      <c r="M241" s="1" t="inlineStr"/>
+      <c r="N241" s="1" t="inlineStr"/>
+      <c r="O241" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P241" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="1" t="n">
+        <v>566804</v>
+      </c>
+      <c r="B242" s="1" t="inlineStr">
+        <is>
+          <t>Filing deadlines for an adjudicated dispute</t>
+        </is>
+      </c>
+      <c r="C242" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/filing-deadlines-adjudicated-dispute</t>
+        </is>
+      </c>
+      <c r="D242" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/delais-depot-pour-reglement-par-processus-decisionnel-formel</t>
+        </is>
+      </c>
+      <c r="E242" s="1" t="inlineStr">
+        <is>
+          <t>Friday, August 26, 2016</t>
+        </is>
+      </c>
+      <c r="F242" s="1" t="n">
+        <v>2017</v>
+      </c>
+      <c r="G242" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H242" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I242" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J242" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K242" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L242" s="1" t="n">
+        <v>87</v>
+      </c>
+      <c r="M242" s="1" t="n">
+        <v>109</v>
+      </c>
+      <c r="N242" s="1" t="n">
+        <v>111</v>
+      </c>
+      <c r="O242" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P242" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="1" t="n">
+        <v>566829</v>
+      </c>
+      <c r="B243" s="1" t="inlineStr">
+        <is>
+          <t>Summary of Roles: Parties and Mediator</t>
+        </is>
+      </c>
+      <c r="C243" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/summary-roles-parties-and-mediator</t>
+        </is>
+      </c>
+      <c r="D243" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/resume-des-roles-parties-et-mediateur</t>
+        </is>
+      </c>
+      <c r="E243" s="1" t="inlineStr">
+        <is>
+          <t>Tuesday, October 20, 2015</t>
+        </is>
+      </c>
+      <c r="F243" s="1" t="n">
+        <v>2017</v>
+      </c>
+      <c r="G243" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H243" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I243" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J243" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K243" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L243" s="1" t="n">
+        <v>61</v>
+      </c>
+      <c r="M243" s="1" t="n">
+        <v>80</v>
+      </c>
+      <c r="N243" s="1" t="n">
+        <v>79</v>
+      </c>
+      <c r="O243" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P243" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="1" t="n">
+        <v>566833</v>
+      </c>
+      <c r="B244" s="1" t="inlineStr">
+        <is>
+          <t>Disputes about the relocation of railway lines or rerouting of traffic in urban areas</t>
+        </is>
+      </c>
+      <c r="C244" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/disputes-about-relocation-railway-lines-or-rerouting-traffic-urban-areas</t>
+        </is>
+      </c>
+      <c r="D244" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/differends-sur-deplacement-lignes-chemin-fer-dans-des-zones-urbaines</t>
+        </is>
+      </c>
+      <c r="E244" s="1" t="inlineStr">
+        <is>
+          <t>Tuesday, October 20, 2015</t>
+        </is>
+      </c>
+      <c r="F244" s="1" t="n">
+        <v>2017</v>
+      </c>
+      <c r="G244" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H244" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I244" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J244" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K244" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L244" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="M244" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="N244" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="O244" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P244" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="1" t="n">
+        <v>566834</v>
+      </c>
+      <c r="B245" s="1" t="inlineStr">
+        <is>
+          <t>Complaints about fares and rates on domestic routes with little or no competition</t>
+        </is>
+      </c>
+      <c r="C245" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/complaints-about-fares-and-rates-domestic-routes-little-or-no-competition</t>
+        </is>
+      </c>
+      <c r="D245" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/plaintes-au-sujet-des-tarifs-et-frais-lies-aux-routes-interieures-ou-concurrence-est-faible-ou-nulle</t>
+        </is>
+      </c>
+      <c r="E245" s="1" t="inlineStr">
+        <is>
+          <t>Tuesday, October 20, 2015</t>
+        </is>
+      </c>
+      <c r="F245" s="1" t="n">
+        <v>2017</v>
+      </c>
+      <c r="G245" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H245" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I245" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J245" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K245" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L245" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="M245" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="N245" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="O245" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P245" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="1" t="n">
+        <v>566836</v>
+      </c>
+      <c r="B246" s="1" t="inlineStr">
+        <is>
+          <t>Table of concordance</t>
+        </is>
+      </c>
+      <c r="C246" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/table-concordance</t>
+        </is>
+      </c>
+      <c r="D246" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/table-concordance</t>
+        </is>
+      </c>
+      <c r="E246" s="1" t="inlineStr">
+        <is>
+          <t>Tuesday, October 20, 2015</t>
+        </is>
+      </c>
+      <c r="F246" s="1" t="n">
+        <v>2017</v>
+      </c>
+      <c r="G246" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H246" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I246" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J246" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K246" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L246" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="M246" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="N246" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="O246" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P246" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="1" t="n">
+        <v>566838</v>
+      </c>
+      <c r="B247" s="1" t="inlineStr">
+        <is>
+          <t>Criteria for Inclusion on the Canadian Transportation Agency’s List of Persons who Agree to Act as Arbitrators</t>
+        </is>
+      </c>
+      <c r="C247" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/criteria-inclusion-canadian-transportation-agencys-list-persons-who-agree-act-arbitrators</t>
+        </is>
+      </c>
+      <c r="D247" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/criteres-dinclusion-a-liste-des-personnes-qui-acceptent-dagir-comme-arbitres-aupres-loffice-des</t>
+        </is>
+      </c>
+      <c r="E247" s="1" t="inlineStr">
+        <is>
+          <t>Tuesday, October 20, 2015</t>
+        </is>
+      </c>
+      <c r="F247" s="1" t="n">
+        <v>2017</v>
+      </c>
+      <c r="G247" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H247" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I247" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J247" s="1" t="inlineStr">
+        <is>
+          <t>Unsure</t>
+        </is>
+      </c>
+      <c r="K247" s="1" t="inlineStr">
+        <is>
+          <t>Duplicate; Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L247" s="1" t="n">
+        <v>104</v>
+      </c>
+      <c r="M247" s="1" t="n">
+        <v>124</v>
+      </c>
+      <c r="N247" s="1" t="n">
+        <v>128</v>
+      </c>
+      <c r="O247" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P247" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="1" t="n">
+        <v>562740</v>
+      </c>
+      <c r="B248" s="1" t="inlineStr">
+        <is>
+          <t>FAQs: Canadian Transportation Agency Rules (Dispute Proceedings and Certain Rules Applicable to All Proceedings)</t>
+        </is>
+      </c>
+      <c r="C248" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/faqs-canadian-transportation-agency-rules-dispute-proceedings-and-certain-rules-applicable-all</t>
+        </is>
+      </c>
+      <c r="D248" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/faq-regles-loffice-des-transports-canada-instances-reglement-des-differends-et-certaines-regles</t>
+        </is>
+      </c>
+      <c r="E248" s="1" t="inlineStr">
+        <is>
+          <t>Tuesday, December 23, 2014</t>
+        </is>
+      </c>
+      <c r="F248" s="1" t="n">
+        <v>2017</v>
+      </c>
+      <c r="G248" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H248" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I248" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J248" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K248" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L248" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="M248" s="1" t="n">
+        <v>41</v>
+      </c>
+      <c r="N248" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="O248" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P248" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="1" t="n">
+        <v>93862</v>
+      </c>
+      <c r="B249" s="1" t="inlineStr">
+        <is>
+          <t>Criteria for Inclusion on the Canadian Transportation Agency’s List of Persons who Agree to Act as Arbitrators</t>
+        </is>
+      </c>
+      <c r="C249" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/criteria-inclusion-canadian-transportation-agencys-list-persons-who-agree-act-arbitrators-0</t>
+        </is>
+      </c>
+      <c r="D249" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/criteres-dinclusion-a-liste-des-personnes-qui-acceptent-dagir-comme-arbitres-aupres-loffice-des-0</t>
+        </is>
+      </c>
+      <c r="E249" s="1" t="inlineStr">
+        <is>
+          <t>Wednesday, November 27, 2013</t>
+        </is>
+      </c>
+      <c r="F249" s="1" t="n">
+        <v>2017</v>
+      </c>
+      <c r="G249" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H249" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I249" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J249" s="1" t="inlineStr">
+        <is>
+          <t>Unsure</t>
+        </is>
+      </c>
+      <c r="K249" s="1" t="inlineStr">
+        <is>
+          <t>Duplicate; Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L249" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="M249" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="N249" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="O249" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P249" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="1" t="n">
+        <v>93850</v>
+      </c>
+      <c r="B250" s="1" t="inlineStr">
+        <is>
+          <t>Highlights of the proposed revised General Rules</t>
+        </is>
+      </c>
+      <c r="C250" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/highlights-proposed-revised-general-rules</t>
+        </is>
+      </c>
+      <c r="D250" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/faits-saillants-des-regles-generales-revisees-proposees</t>
+        </is>
+      </c>
+      <c r="E250" s="1" t="inlineStr">
+        <is>
+          <t>Monday, December 16, 2013</t>
+        </is>
+      </c>
+      <c r="F250" s="1" t="n">
+        <v>2017</v>
+      </c>
+      <c r="G250" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H250" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I250" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J250" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K250" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L250" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="M250" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="N250" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="O250" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P250" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="1" t="n">
+        <v>93848</v>
+      </c>
+      <c r="B251" s="1" t="inlineStr">
+        <is>
+          <t>Revision of the Canadian Transportation Agency General Rules: Considerations</t>
+        </is>
+      </c>
+      <c r="C251" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/revision-canadian-transportation-agency-general-rules-considerations</t>
+        </is>
+      </c>
+      <c r="D251" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/revision-des-regles-generales-loffice-des-transports-canada-facteurs-a-considerer</t>
+        </is>
+      </c>
+      <c r="E251" s="1" t="inlineStr">
+        <is>
+          <t>Wednesday, January 22, 2014</t>
+        </is>
+      </c>
+      <c r="F251" s="1" t="n">
+        <v>2017</v>
+      </c>
+      <c r="G251" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H251" s="1" t="inlineStr">
+        <is>
+          <t>Complaint and Dispute Resolution</t>
+        </is>
+      </c>
+      <c r="I251" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J251" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K251" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L251" s="1" t="inlineStr"/>
+      <c r="M251" s="1" t="inlineStr"/>
+      <c r="N251" s="1" t="inlineStr"/>
+      <c r="O251" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P251" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
